--- a/output/yearly_total_coral_cover_iteration_53_growth_param_0.5.xlsx
+++ b/output/yearly_total_coral_cover_iteration_53_growth_param_0.5.xlsx
@@ -477,16 +477,16 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>1.287568431877815</v>
+        <v>1.261051426386109</v>
       </c>
       <c r="C3" t="n">
-        <v>4.612964336192664</v>
+        <v>4.627710186710451</v>
       </c>
       <c r="D3" t="n">
-        <v>6.115429262151053</v>
+        <v>6.198298585866525</v>
       </c>
       <c r="E3" t="n">
-        <v>12.01596203022153</v>
+        <v>12.08706019896309</v>
       </c>
     </row>
     <row r="4">
@@ -494,16 +494,16 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>1.46259285458309</v>
+        <v>1.393711085185994</v>
       </c>
       <c r="C4" t="n">
-        <v>5.085495929149239</v>
+        <v>5.129208356515001</v>
       </c>
       <c r="D4" t="n">
-        <v>6.328576106008083</v>
+        <v>6.505063459277689</v>
       </c>
       <c r="E4" t="n">
-        <v>12.87666488974041</v>
+        <v>13.02798290097868</v>
       </c>
     </row>
     <row r="5">
@@ -511,16 +511,16 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>1.694350184426121</v>
+        <v>1.585952050994234</v>
       </c>
       <c r="C5" t="n">
-        <v>5.665083057556371</v>
+        <v>5.78647389814595</v>
       </c>
       <c r="D5" t="n">
-        <v>6.573261976023392</v>
+        <v>6.837490393923702</v>
       </c>
       <c r="E5" t="n">
-        <v>13.93269521800588</v>
+        <v>14.20991634306389</v>
       </c>
     </row>
     <row r="6">
@@ -528,16 +528,16 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>1.960665782588709</v>
+        <v>1.804820934459853</v>
       </c>
       <c r="C6" t="n">
-        <v>6.352233956830779</v>
+        <v>6.63442380732055</v>
       </c>
       <c r="D6" t="n">
-        <v>6.944811916252227</v>
+        <v>7.202856001568522</v>
       </c>
       <c r="E6" t="n">
-        <v>15.25771165567172</v>
+        <v>15.64210074334892</v>
       </c>
     </row>
     <row r="7">
@@ -545,16 +545,16 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>2.253173864749932</v>
+        <v>2.053929583670995</v>
       </c>
       <c r="C7" t="n">
-        <v>7.11102606978613</v>
+        <v>7.679016088539016</v>
       </c>
       <c r="D7" t="n">
-        <v>7.268619820981432</v>
+        <v>7.551948750809352</v>
       </c>
       <c r="E7" t="n">
-        <v>16.6328197555175</v>
+        <v>17.28489442301936</v>
       </c>
     </row>
     <row r="8">
@@ -562,16 +562,16 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>1.448528788466296</v>
+        <v>1.271624780151203</v>
       </c>
       <c r="C8" t="n">
-        <v>4.720639110686436</v>
+        <v>5.496531411060073</v>
       </c>
       <c r="D8" t="n">
-        <v>5.490079914872523</v>
+        <v>5.731563585400558</v>
       </c>
       <c r="E8" t="n">
-        <v>11.65924781402525</v>
+        <v>12.49971977661183</v>
       </c>
     </row>
     <row r="9">
@@ -579,16 +579,16 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>1.850010957322996</v>
+        <v>1.598238082395267</v>
       </c>
       <c r="C9" t="n">
-        <v>5.739900575125931</v>
+        <v>6.943561734932728</v>
       </c>
       <c r="D9" t="n">
-        <v>5.950263592779568</v>
+        <v>6.217171567626774</v>
       </c>
       <c r="E9" t="n">
-        <v>13.5401751252285</v>
+        <v>14.75897138495477</v>
       </c>
     </row>
     <row r="10">
@@ -596,16 +596,16 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>2.276153113773665</v>
+        <v>1.937455275178283</v>
       </c>
       <c r="C10" t="n">
-        <v>6.949154863565362</v>
+        <v>8.564759169521828</v>
       </c>
       <c r="D10" t="n">
-        <v>6.377276521063164</v>
+        <v>6.694808823442315</v>
       </c>
       <c r="E10" t="n">
-        <v>15.60258449840219</v>
+        <v>17.19702326814243</v>
       </c>
     </row>
     <row r="11">
@@ -613,16 +613,16 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>2.700089133937986</v>
+        <v>2.28220530845906</v>
       </c>
       <c r="C11" t="n">
-        <v>8.358206342274054</v>
+        <v>10.27000359851903</v>
       </c>
       <c r="D11" t="n">
-        <v>6.805368795623467</v>
+        <v>7.164387554293237</v>
       </c>
       <c r="E11" t="n">
-        <v>17.86366427183551</v>
+        <v>19.71659646127132</v>
       </c>
     </row>
     <row r="12">
@@ -630,16 +630,16 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>3.136235482053347</v>
+        <v>2.610620990299007</v>
       </c>
       <c r="C12" t="n">
-        <v>9.898942757494892</v>
+        <v>12.03001614725784</v>
       </c>
       <c r="D12" t="n">
-        <v>7.202515001682049</v>
+        <v>7.558603244459952</v>
       </c>
       <c r="E12" t="n">
-        <v>20.23769324123029</v>
+        <v>22.1992403820168</v>
       </c>
     </row>
     <row r="13">
@@ -647,16 +647,16 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>3.560738402827134</v>
+        <v>2.91648323572859</v>
       </c>
       <c r="C13" t="n">
-        <v>11.57540131553047</v>
+        <v>13.81571162402968</v>
       </c>
       <c r="D13" t="n">
-        <v>7.607006051286669</v>
+        <v>7.943040177260687</v>
       </c>
       <c r="E13" t="n">
-        <v>22.74314576964427</v>
+        <v>24.67523503701896</v>
       </c>
     </row>
     <row r="14">
@@ -664,16 +664,16 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>2.056879250121578</v>
+        <v>1.669560145842126</v>
       </c>
       <c r="C14" t="n">
-        <v>8.22795878695322</v>
+        <v>9.513429778462866</v>
       </c>
       <c r="D14" t="n">
-        <v>5.770624648269369</v>
+        <v>5.992921780941974</v>
       </c>
       <c r="E14" t="n">
-        <v>16.05546268534417</v>
+        <v>17.17591170524697</v>
       </c>
     </row>
     <row r="15">
@@ -681,16 +681,16 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>2.122263647224415</v>
+        <v>1.693622782073215</v>
       </c>
       <c r="C15" t="n">
-        <v>9.096206639112058</v>
+        <v>10.36687287524166</v>
       </c>
       <c r="D15" t="n">
-        <v>5.717502279992574</v>
+        <v>5.952336330848412</v>
       </c>
       <c r="E15" t="n">
-        <v>16.93597256632905</v>
+        <v>18.01283198816329</v>
       </c>
     </row>
     <row r="16">
@@ -698,16 +698,16 @@
         <v>14</v>
       </c>
       <c r="B16" t="n">
-        <v>2.479619811570254</v>
+        <v>1.950271266917416</v>
       </c>
       <c r="C16" t="n">
-        <v>10.94788098409197</v>
+        <v>12.3188818355956</v>
       </c>
       <c r="D16" t="n">
-        <v>6.091224178568208</v>
+        <v>6.318371144899793</v>
       </c>
       <c r="E16" t="n">
-        <v>19.51872497423043</v>
+        <v>20.58752424741281</v>
       </c>
     </row>
     <row r="17">
@@ -715,16 +715,16 @@
         <v>15</v>
       </c>
       <c r="B17" t="n">
-        <v>1.993585975628786</v>
+        <v>1.554185155639041</v>
       </c>
       <c r="C17" t="n">
-        <v>10.29112122238198</v>
+        <v>11.39931803093578</v>
       </c>
       <c r="D17" t="n">
-        <v>5.579242750803497</v>
+        <v>5.809010983505419</v>
       </c>
       <c r="E17" t="n">
-        <v>17.86394994881426</v>
+        <v>18.76251417008024</v>
       </c>
     </row>
     <row r="18">
@@ -732,16 +732,16 @@
         <v>16</v>
       </c>
       <c r="B18" t="n">
-        <v>2.293657161431823</v>
+        <v>1.755443435009637</v>
       </c>
       <c r="C18" t="n">
-        <v>12.13143674642375</v>
+        <v>13.34159787154063</v>
       </c>
       <c r="D18" t="n">
-        <v>5.951433122960505</v>
+        <v>6.189830917982757</v>
       </c>
       <c r="E18" t="n">
-        <v>20.37652703081608</v>
+        <v>21.28687222453302</v>
       </c>
     </row>
     <row r="19">
@@ -749,16 +749,16 @@
         <v>17</v>
       </c>
       <c r="B19" t="n">
-        <v>2.315775937208504</v>
+        <v>1.745753585168721</v>
       </c>
       <c r="C19" t="n">
-        <v>13.09497303075679</v>
+        <v>14.28718780784002</v>
       </c>
       <c r="D19" t="n">
-        <v>5.989701648472045</v>
+        <v>6.224624056621265</v>
       </c>
       <c r="E19" t="n">
-        <v>21.40045061643733</v>
+        <v>22.25756544963001</v>
       </c>
     </row>
     <row r="20">
@@ -766,16 +766,16 @@
         <v>18</v>
       </c>
       <c r="B20" t="n">
-        <v>2.590459127379719</v>
+        <v>1.93214820429702</v>
       </c>
       <c r="C20" t="n">
-        <v>15.12282200126378</v>
+        <v>16.46186696499418</v>
       </c>
       <c r="D20" t="n">
-        <v>6.301131655213219</v>
+        <v>6.572869602271694</v>
       </c>
       <c r="E20" t="n">
-        <v>24.01441278385672</v>
+        <v>24.96688477156289</v>
       </c>
     </row>
     <row r="21">
@@ -783,16 +783,16 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>1.549934188079652</v>
+        <v>1.141036269260856</v>
       </c>
       <c r="C21" t="n">
-        <v>11.12059985770011</v>
+        <v>12.11552261613791</v>
       </c>
       <c r="D21" t="n">
-        <v>5.204863081266018</v>
+        <v>5.432118039845069</v>
       </c>
       <c r="E21" t="n">
-        <v>17.87539712704578</v>
+        <v>18.68867692524384</v>
       </c>
     </row>
   </sheetData>

--- a/output/yearly_total_coral_cover_iteration_53_growth_param_0.5.xlsx
+++ b/output/yearly_total_coral_cover_iteration_53_growth_param_0.5.xlsx
@@ -477,16 +477,16 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>1.261051426386109</v>
+        <v>1.261748467256124</v>
       </c>
       <c r="C3" t="n">
-        <v>4.627710186710451</v>
+        <v>4.613357035274363</v>
       </c>
       <c r="D3" t="n">
-        <v>6.198298585866525</v>
+        <v>6.059302745899263</v>
       </c>
       <c r="E3" t="n">
-        <v>12.08706019896309</v>
+        <v>11.93440824842975</v>
       </c>
     </row>
     <row r="4">
@@ -494,16 +494,16 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>1.393711085185994</v>
+        <v>1.393226747328588</v>
       </c>
       <c r="C4" t="n">
-        <v>5.129208356515001</v>
+        <v>5.10463477941343</v>
       </c>
       <c r="D4" t="n">
-        <v>6.505063459277689</v>
+        <v>6.340191828761632</v>
       </c>
       <c r="E4" t="n">
-        <v>13.02798290097868</v>
+        <v>12.83805335550365</v>
       </c>
     </row>
     <row r="5">
@@ -511,16 +511,16 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>1.585952050994234</v>
+        <v>1.578880782694369</v>
       </c>
       <c r="C5" t="n">
-        <v>5.78647389814595</v>
+        <v>5.7430269178981</v>
       </c>
       <c r="D5" t="n">
-        <v>6.837490393923702</v>
+        <v>6.657471402552607</v>
       </c>
       <c r="E5" t="n">
-        <v>14.20991634306389</v>
+        <v>13.97937910314508</v>
       </c>
     </row>
     <row r="6">
@@ -528,16 +528,16 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>1.804820934459853</v>
+        <v>1.781385192346899</v>
       </c>
       <c r="C6" t="n">
-        <v>6.63442380732055</v>
+        <v>6.533041813958678</v>
       </c>
       <c r="D6" t="n">
-        <v>7.202856001568522</v>
+        <v>7.020941431134959</v>
       </c>
       <c r="E6" t="n">
-        <v>15.64210074334892</v>
+        <v>15.33536843744054</v>
       </c>
     </row>
     <row r="7">
@@ -545,16 +545,16 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>2.053929583670995</v>
+        <v>2.000905388983279</v>
       </c>
       <c r="C7" t="n">
-        <v>7.679016088539016</v>
+        <v>7.465220415779404</v>
       </c>
       <c r="D7" t="n">
-        <v>7.551948750809352</v>
+        <v>7.415067664811208</v>
       </c>
       <c r="E7" t="n">
-        <v>17.28489442301936</v>
+        <v>16.88119346957389</v>
       </c>
     </row>
     <row r="8">
@@ -562,16 +562,16 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>1.271624780151203</v>
+        <v>1.204143796486683</v>
       </c>
       <c r="C8" t="n">
-        <v>5.496531411060073</v>
+        <v>5.124320493972229</v>
       </c>
       <c r="D8" t="n">
-        <v>5.731563585400558</v>
+        <v>5.703930206578995</v>
       </c>
       <c r="E8" t="n">
-        <v>12.49971977661183</v>
+        <v>12.03239449703791</v>
       </c>
     </row>
     <row r="9">
@@ -579,16 +579,16 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>1.598238082395267</v>
+        <v>1.489106846596801</v>
       </c>
       <c r="C9" t="n">
-        <v>6.943561734932728</v>
+        <v>6.294729142802367</v>
       </c>
       <c r="D9" t="n">
-        <v>6.217171567626774</v>
+        <v>6.226520357678706</v>
       </c>
       <c r="E9" t="n">
-        <v>14.75897138495477</v>
+        <v>14.01035634707787</v>
       </c>
     </row>
     <row r="10">
@@ -596,16 +596,16 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>1.937455275178283</v>
+        <v>1.788463216223338</v>
       </c>
       <c r="C10" t="n">
-        <v>8.564759169521828</v>
+        <v>7.643861923894289</v>
       </c>
       <c r="D10" t="n">
-        <v>6.694808823442315</v>
+        <v>6.772207262061846</v>
       </c>
       <c r="E10" t="n">
-        <v>17.19702326814243</v>
+        <v>16.20453240217947</v>
       </c>
     </row>
     <row r="11">
@@ -613,16 +613,16 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>2.28220530845906</v>
+        <v>2.100634475809986</v>
       </c>
       <c r="C11" t="n">
-        <v>10.27000359851903</v>
+        <v>9.119335948674983</v>
       </c>
       <c r="D11" t="n">
-        <v>7.164387554293237</v>
+        <v>7.262344678049602</v>
       </c>
       <c r="E11" t="n">
-        <v>19.71659646127132</v>
+        <v>18.48231510253457</v>
       </c>
     </row>
     <row r="12">
@@ -630,16 +630,16 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>2.610620990299007</v>
+        <v>2.42293518344816</v>
       </c>
       <c r="C12" t="n">
-        <v>12.03001614725784</v>
+        <v>10.66098064660632</v>
       </c>
       <c r="D12" t="n">
-        <v>7.558603244459952</v>
+        <v>7.819325341046707</v>
       </c>
       <c r="E12" t="n">
-        <v>22.1992403820168</v>
+        <v>20.90324117110119</v>
       </c>
     </row>
     <row r="13">
@@ -647,16 +647,16 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>2.91648323572859</v>
+        <v>2.725265498034338</v>
       </c>
       <c r="C13" t="n">
-        <v>13.81571162402968</v>
+        <v>12.25206260616932</v>
       </c>
       <c r="D13" t="n">
-        <v>7.943040177260687</v>
+        <v>8.32822579152236</v>
       </c>
       <c r="E13" t="n">
-        <v>24.67523503701896</v>
+        <v>23.30555389572602</v>
       </c>
     </row>
     <row r="14">
@@ -664,16 +664,16 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>1.669560145842126</v>
+        <v>1.581261757322167</v>
       </c>
       <c r="C14" t="n">
-        <v>9.513429778462866</v>
+        <v>8.581662849839262</v>
       </c>
       <c r="D14" t="n">
-        <v>5.992921780941974</v>
+        <v>6.323760939796107</v>
       </c>
       <c r="E14" t="n">
-        <v>17.17591170524697</v>
+        <v>16.48668554695753</v>
       </c>
     </row>
     <row r="15">
@@ -681,16 +681,16 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>1.693622782073215</v>
+        <v>1.604470273050562</v>
       </c>
       <c r="C15" t="n">
-        <v>10.36687287524166</v>
+        <v>9.264429108234749</v>
       </c>
       <c r="D15" t="n">
-        <v>5.952336330848412</v>
+        <v>6.381850951456391</v>
       </c>
       <c r="E15" t="n">
-        <v>18.01283198816329</v>
+        <v>17.2507503327417</v>
       </c>
     </row>
     <row r="16">
@@ -698,16 +698,16 @@
         <v>14</v>
       </c>
       <c r="B16" t="n">
-        <v>1.950271266917416</v>
+        <v>1.85832077693766</v>
       </c>
       <c r="C16" t="n">
-        <v>12.3188818355956</v>
+        <v>10.92321948176129</v>
       </c>
       <c r="D16" t="n">
-        <v>6.318371144899793</v>
+        <v>6.860020988286844</v>
       </c>
       <c r="E16" t="n">
-        <v>20.58752424741281</v>
+        <v>19.64156124698579</v>
       </c>
     </row>
     <row r="17">
@@ -715,16 +715,16 @@
         <v>15</v>
       </c>
       <c r="B17" t="n">
-        <v>1.554185155639041</v>
+        <v>1.491628191924434</v>
       </c>
       <c r="C17" t="n">
-        <v>11.39931803093578</v>
+        <v>10.05072066204306</v>
       </c>
       <c r="D17" t="n">
-        <v>5.809010983505419</v>
+        <v>6.375253606883852</v>
       </c>
       <c r="E17" t="n">
-        <v>18.76251417008024</v>
+        <v>17.91760246085135</v>
       </c>
     </row>
     <row r="18">
@@ -732,16 +732,16 @@
         <v>16</v>
       </c>
       <c r="B18" t="n">
-        <v>1.755443435009637</v>
+        <v>1.706621121677443</v>
       </c>
       <c r="C18" t="n">
-        <v>13.34159787154063</v>
+        <v>11.71408597987139</v>
       </c>
       <c r="D18" t="n">
-        <v>6.189830917982757</v>
+        <v>6.807242231706534</v>
       </c>
       <c r="E18" t="n">
-        <v>21.28687222453302</v>
+        <v>20.22794933325537</v>
       </c>
     </row>
     <row r="19">
@@ -749,16 +749,16 @@
         <v>17</v>
       </c>
       <c r="B19" t="n">
-        <v>1.745753585168721</v>
+        <v>1.717273084268521</v>
       </c>
       <c r="C19" t="n">
-        <v>14.28718780784002</v>
+        <v>12.51603640956244</v>
       </c>
       <c r="D19" t="n">
-        <v>6.224624056621265</v>
+        <v>6.924934146491642</v>
       </c>
       <c r="E19" t="n">
-        <v>22.25756544963001</v>
+        <v>21.1582436403226</v>
       </c>
     </row>
     <row r="20">
@@ -766,16 +766,16 @@
         <v>18</v>
       </c>
       <c r="B20" t="n">
-        <v>1.93214820429702</v>
+        <v>1.915802105021311</v>
       </c>
       <c r="C20" t="n">
-        <v>16.46186696499418</v>
+        <v>14.33880810212932</v>
       </c>
       <c r="D20" t="n">
-        <v>6.572869602271694</v>
+        <v>7.318968405068141</v>
       </c>
       <c r="E20" t="n">
-        <v>24.96688477156289</v>
+        <v>23.57357861221877</v>
       </c>
     </row>
     <row r="21">
@@ -783,16 +783,16 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>1.141036269260856</v>
+        <v>1.145876285442792</v>
       </c>
       <c r="C21" t="n">
-        <v>12.11552261613791</v>
+        <v>10.50515203938483</v>
       </c>
       <c r="D21" t="n">
-        <v>5.432118039845069</v>
+        <v>6.102043038269008</v>
       </c>
       <c r="E21" t="n">
-        <v>18.68867692524384</v>
+        <v>17.75307136309662</v>
       </c>
     </row>
   </sheetData>

--- a/output/yearly_total_coral_cover_iteration_53_growth_param_0.5.xlsx
+++ b/output/yearly_total_coral_cover_iteration_53_growth_param_0.5.xlsx
@@ -477,16 +477,16 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>1.261748467256124</v>
+        <v>2.583046454096185</v>
       </c>
       <c r="C3" t="n">
-        <v>4.613357035274363</v>
+        <v>7.761105470509241</v>
       </c>
       <c r="D3" t="n">
-        <v>6.059302745899263</v>
+        <v>8.288334075821821</v>
       </c>
       <c r="E3" t="n">
-        <v>11.93440824842975</v>
+        <v>18.63248600042725</v>
       </c>
     </row>
     <row r="4">
@@ -494,16 +494,16 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>1.393226747328588</v>
+        <v>1.074734139264204</v>
       </c>
       <c r="C4" t="n">
-        <v>5.10463477941343</v>
+        <v>4.632144901158906</v>
       </c>
       <c r="D4" t="n">
-        <v>6.340191828761632</v>
+        <v>5.894883486862161</v>
       </c>
       <c r="E4" t="n">
-        <v>12.83805335550365</v>
+        <v>11.60176252728527</v>
       </c>
     </row>
     <row r="5">
@@ -511,16 +511,16 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>1.578880782694369</v>
+        <v>1.180144512816577</v>
       </c>
       <c r="C5" t="n">
-        <v>5.7430269178981</v>
+        <v>5.408207882858489</v>
       </c>
       <c r="D5" t="n">
-        <v>6.657471402552607</v>
+        <v>6.197297436111945</v>
       </c>
       <c r="E5" t="n">
-        <v>13.97937910314508</v>
+        <v>12.78564983178701</v>
       </c>
     </row>
     <row r="6">
@@ -528,16 +528,16 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>1.781385192346899</v>
+        <v>1.297947858231767</v>
       </c>
       <c r="C6" t="n">
-        <v>6.533041813958678</v>
+        <v>6.408477923648562</v>
       </c>
       <c r="D6" t="n">
-        <v>7.020941431134959</v>
+        <v>6.550624644439825</v>
       </c>
       <c r="E6" t="n">
-        <v>15.33536843744054</v>
+        <v>14.25705042632015</v>
       </c>
     </row>
     <row r="7">
@@ -545,16 +545,16 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>2.000905388983279</v>
+        <v>1.413669086240266</v>
       </c>
       <c r="C7" t="n">
-        <v>7.465220415779404</v>
+        <v>7.570233777874622</v>
       </c>
       <c r="D7" t="n">
-        <v>7.415067664811208</v>
+        <v>6.899082974077356</v>
       </c>
       <c r="E7" t="n">
-        <v>16.88119346957389</v>
+        <v>15.88298583819224</v>
       </c>
     </row>
     <row r="8">
@@ -562,16 +562,16 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>1.204143796486683</v>
+        <v>1.527958440669864</v>
       </c>
       <c r="C8" t="n">
-        <v>5.124320493972229</v>
+        <v>8.914351167298204</v>
       </c>
       <c r="D8" t="n">
-        <v>5.703930206578995</v>
+        <v>7.242737091755451</v>
       </c>
       <c r="E8" t="n">
-        <v>12.03239449703791</v>
+        <v>17.68504669972352</v>
       </c>
     </row>
     <row r="9">
@@ -579,16 +579,16 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>1.489106846596801</v>
+        <v>1.625618077544805</v>
       </c>
       <c r="C9" t="n">
-        <v>6.294729142802367</v>
+        <v>10.3815715860908</v>
       </c>
       <c r="D9" t="n">
-        <v>6.226520357678706</v>
+        <v>7.588242453072386</v>
       </c>
       <c r="E9" t="n">
-        <v>14.01035634707787</v>
+        <v>19.59543211670799</v>
       </c>
     </row>
     <row r="10">
@@ -596,16 +596,16 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>1.788463216223338</v>
+        <v>1.01340906770877</v>
       </c>
       <c r="C10" t="n">
-        <v>7.643861923894289</v>
+        <v>7.538860255865342</v>
       </c>
       <c r="D10" t="n">
-        <v>6.772207262061846</v>
+        <v>5.932063240755714</v>
       </c>
       <c r="E10" t="n">
-        <v>16.20453240217947</v>
+        <v>14.48433256432983</v>
       </c>
     </row>
     <row r="11">
@@ -613,16 +613,16 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>2.100634475809986</v>
+        <v>0.9323265248150259</v>
       </c>
       <c r="C11" t="n">
-        <v>9.119335948674983</v>
+        <v>8.16832743139727</v>
       </c>
       <c r="D11" t="n">
-        <v>7.262344678049602</v>
+        <v>5.752462315740803</v>
       </c>
       <c r="E11" t="n">
-        <v>18.48231510253457</v>
+        <v>14.8531162719531</v>
       </c>
     </row>
     <row r="12">
@@ -630,16 +630,16 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>2.42293518344816</v>
+        <v>0.9920069677561896</v>
       </c>
       <c r="C12" t="n">
-        <v>10.66098064660632</v>
+        <v>9.821826184797917</v>
       </c>
       <c r="D12" t="n">
-        <v>7.819325341046707</v>
+        <v>6.08499008064624</v>
       </c>
       <c r="E12" t="n">
-        <v>20.90324117110119</v>
+        <v>16.89882323320035</v>
       </c>
     </row>
     <row r="13">
@@ -647,16 +647,16 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>2.725265498034338</v>
+        <v>0.77876154891674</v>
       </c>
       <c r="C13" t="n">
-        <v>12.25206260616932</v>
+        <v>9.492430195069028</v>
       </c>
       <c r="D13" t="n">
-        <v>8.32822579152236</v>
+        <v>5.502862779413094</v>
       </c>
       <c r="E13" t="n">
-        <v>23.30555389572602</v>
+        <v>15.77405452339886</v>
       </c>
     </row>
     <row r="14">
@@ -664,16 +664,16 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>1.581261757322167</v>
+        <v>0.8320213618721293</v>
       </c>
       <c r="C14" t="n">
-        <v>8.581662849839262</v>
+        <v>11.31232536686247</v>
       </c>
       <c r="D14" t="n">
-        <v>6.323760939796107</v>
+        <v>5.771351141570511</v>
       </c>
       <c r="E14" t="n">
-        <v>16.48668554695753</v>
+        <v>17.91569787030511</v>
       </c>
     </row>
     <row r="15">
@@ -681,16 +681,16 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>1.604470273050562</v>
+        <v>0.797346032958132</v>
       </c>
       <c r="C15" t="n">
-        <v>9.264429108234749</v>
+        <v>12.39403462235569</v>
       </c>
       <c r="D15" t="n">
-        <v>6.381850951456391</v>
+        <v>5.758166269902477</v>
       </c>
       <c r="E15" t="n">
-        <v>17.2507503327417</v>
+        <v>18.9495469252163</v>
       </c>
     </row>
     <row r="16">
@@ -698,16 +698,16 @@
         <v>14</v>
       </c>
       <c r="B16" t="n">
-        <v>1.85832077693766</v>
+        <v>0.8654400537246907</v>
       </c>
       <c r="C16" t="n">
-        <v>10.92321948176129</v>
+        <v>14.55919082677864</v>
       </c>
       <c r="D16" t="n">
-        <v>6.860020988286844</v>
+        <v>6.080856922811361</v>
       </c>
       <c r="E16" t="n">
-        <v>19.64156124698579</v>
+        <v>21.50548780331469</v>
       </c>
     </row>
     <row r="17">
@@ -715,16 +715,16 @@
         <v>15</v>
       </c>
       <c r="B17" t="n">
-        <v>1.491628191924434</v>
+        <v>0.5179700887606172</v>
       </c>
       <c r="C17" t="n">
-        <v>10.05072066204306</v>
+        <v>10.9548710277462</v>
       </c>
       <c r="D17" t="n">
-        <v>6.375253606883852</v>
+        <v>4.993384808294212</v>
       </c>
       <c r="E17" t="n">
-        <v>17.91760246085135</v>
+        <v>16.46622592480103</v>
       </c>
     </row>
     <row r="18">
@@ -732,16 +732,16 @@
         <v>16</v>
       </c>
       <c r="B18" t="n">
-        <v>1.706621121677443</v>
+        <v>0.4037142909403734</v>
       </c>
       <c r="C18" t="n">
-        <v>11.71408597987139</v>
+        <v>10.00321389063456</v>
       </c>
       <c r="D18" t="n">
-        <v>6.807242231706534</v>
+        <v>4.449889279223178</v>
       </c>
       <c r="E18" t="n">
-        <v>20.22794933325537</v>
+        <v>14.85681746079811</v>
       </c>
     </row>
     <row r="19">
@@ -749,16 +749,16 @@
         <v>17</v>
       </c>
       <c r="B19" t="n">
-        <v>1.717273084268521</v>
+        <v>0.4671253751576749</v>
       </c>
       <c r="C19" t="n">
-        <v>12.51603640956244</v>
+        <v>12.42281946504421</v>
       </c>
       <c r="D19" t="n">
-        <v>6.924934146491642</v>
+        <v>4.871599005582396</v>
       </c>
       <c r="E19" t="n">
-        <v>21.1582436403226</v>
+        <v>17.76154384578428</v>
       </c>
     </row>
     <row r="20">
@@ -766,16 +766,16 @@
         <v>18</v>
       </c>
       <c r="B20" t="n">
-        <v>1.915802105021311</v>
+        <v>0.5266094685579891</v>
       </c>
       <c r="C20" t="n">
-        <v>14.33880810212932</v>
+        <v>15.00944977637736</v>
       </c>
       <c r="D20" t="n">
-        <v>7.318968405068141</v>
+        <v>5.25423517331259</v>
       </c>
       <c r="E20" t="n">
-        <v>23.57357861221877</v>
+        <v>20.79029441824794</v>
       </c>
     </row>
     <row r="21">
@@ -783,16 +783,16 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>1.145876285442792</v>
+        <v>0.5777585239492479</v>
       </c>
       <c r="C21" t="n">
-        <v>10.50515203938483</v>
+        <v>17.61249490932552</v>
       </c>
       <c r="D21" t="n">
-        <v>6.102043038269008</v>
+        <v>5.583699885380777</v>
       </c>
       <c r="E21" t="n">
-        <v>17.75307136309662</v>
+        <v>23.77395331865555</v>
       </c>
     </row>
   </sheetData>
